--- a/src/test/resources/testdata/InsuranceApplication_TestData.xlsx
+++ b/src/test/resources/testdata/InsuranceApplication_TestData.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="44" documentId="11_CE31C22AAE8218C6DE3B7E9237F5FEBFBDC72E0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAF37A67-276E-452E-8F80-37206064261B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Travel" sheetId="1" r:id="rId1"/>
